--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Students/AdminApp_Students_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Students/AdminApp_Students_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="498">
   <si>
     <t>S.No.</t>
   </si>
@@ -616,6 +616,12 @@
     <t>Verified live 2026-08-22. Note the heading format is “Last name, First name”, and for an email-based account the identifier line holds the email.</t>
   </si>
   <si>
+    <t>As expected — automated</t>
+  </si>
+  <si>
+    <t>Automated (adminStudentProfileTest_thor). Passing on Thor 2026-09-15: baseline 10/10, then 11/11 after TST_SPRF_TC_12 was added.</t>
+  </si>
+  <si>
     <t>TST_SPRF_TC_4</t>
   </si>
   <si>
@@ -635,6 +641,9 @@
   </si>
   <si>
     <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-22. “Code expired” was seen only on this account — a fixture worth keeping. The “(N)” in “Course materials (N)” counts UMBRELLAS, not components.</t>
+  </si>
+  <si>
+    <t>Automated (adminStudentProfileTest_thor). Passing on Thor 2026-09-15: baseline 10/10, then 11/11.</t>
   </si>
   <si>
     <t>TST_SPRF_TC_5</t>
@@ -690,6 +699,12 @@
   </si>
   <si>
     <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. DEFECT — raise. Two faults in one: the 500 itself (student-specific: other profiles on the same school load fine) and the missing client-side error handling for it. Evidence: screenshot profile-blank.png + console/network trace, Thor 2026-08-22.</t>
+  </si>
+  <si>
+    <t>On Hold</t>
+  </si>
+  <si>
+    <t>On Hold in automation — open bug: the profile hangs on an empty page because getUserDetailWithClasses returns HTTP 500. Case asserts the requirement and is kept OUT of adminStudentProfile.json. Add it back when fixed.</t>
   </si>
   <si>
     <t>TST_SPRF_TC_2</t>
@@ -855,17 +870,22 @@
     <t>Verify a required name field cannot be saved empty</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Clear the First name field.
-2. Click "Update".</t>
+    <t>1. Clear the First name field. 2. Move focus out of the field (Tab). 3. Read the message under First name and the state of Update. Do not force a submit.</t>
   </si>
   <si>
     <t>First name: (empty)</t>
   </si>
   <si>
-    <t>[ASSUMED] The update is refused and a required-field validation message is shown against First name.</t>
+    <t>The update cannot be submitted. When the empty First name field is left, the message This field is required is shown under it, and Update is blocked: greyed to 50% opacity, removed from the tab order and not clickable (pointer-events none). Update has NO disabled attribute. Nothing is saved. Verified live 2026-09-15.</t>
   </si>
   <si>
     <t>The field carries the HTML required attribute (captured live 2026-08-22) but the message text was not triggered. Capture the verbatim copy during Phase 1.</t>
+  </si>
+  <si>
+    <t>As expected — automated. Update is never clicked.</t>
+  </si>
+  <si>
+    <t>Automated (adminStudentProfileTest_thor). 2 consecutive clean runs on Thor 2026-09-15, on Marvin Jae student. Resolves the earlier [ASSUMED] result and captures the verbatim copy. Automation note: Update is blocked by CSS only, so a native disabled check would wrongly read it as enabled.</t>
   </si>
   <si>
     <t>TST_SPRF_TC_14</t>
@@ -1010,6 +1030,9 @@
     <t>DESTRUCTIVE and asynchronous, reported by email rather than in-app. All dialog copy was captured free from the pre-rendered DOM 2026-08-22 without triggering anything (admin-shared.md §A6). Never run against a pre-existing student on this shared school. Removal is also reachable from the profile via Manage account.</t>
   </si>
   <si>
+    <t>On Hold in automation — student removal is missing from the Students tab (profile and list). Awaiting product: withdrawn on purpose, or a regression? See PRODUCT-QUESTIONS_students-tab_2026-09-16.md issue 1.</t>
+  </si>
+  <si>
     <t>TST_SPRF_TC_20</t>
   </si>
   <si>
@@ -1032,7 +1055,7 @@
     <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. BLOCKED at design time on FCN-CHZ-PDA — the school holds 26 students, so 51 cannot be selected. The modal copy is nevertheless verified word for word from the pre-rendered DOM (2026-08-22), so this case is short work once a school with 51+ students exists. Unblocked by &lt;SCHOOL_WITH_51_PLUS_STUDENTS&gt;.</t>
   </si>
   <si>
-    <t>Blocked at design time. The 50-student removal cap needs 51+ students selected; FCN-CHZ-PDA holds 26. Modal copy is already verified word for word from the pre-rendered DOM, so this is short work once a larger school exists.</t>
+    <t>Blocked. 2026-09-15: student removal is absent from the Students tab entirely (see TST_SPRF_TC_19), awaiting product. Original design-time reason still applies: the 50-student cap needs 51+ students; FCN-CHZ-PDA holds 27.</t>
   </si>
   <si>
     <t>TST_SPRF_TC_21</t>
@@ -1048,6 +1071,9 @@
   </si>
   <si>
     <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-22 — natively disabled.</t>
+  </si>
+  <si>
+    <t>On Hold in automation — the list has no Remove button or selection controls, so there is nothing to assert. Awaiting product; see PRODUCT-QUESTIONS_students-tab_2026-09-16.md issue 1.</t>
   </si>
   <si>
     <t>TST_SPRF_TC_22</t>
@@ -1070,6 +1096,9 @@
   </si>
   <si>
     <t>Not run 2026-08-22 (would require opening a destructive dialog against a real shared account). Also confirm whether the row selection survives the cancel.</t>
+  </si>
+  <si>
+    <t>On Hold in automation — no removal confirmation exists to cancel. Awaiting product; see PRODUCT-QUESTIONS_students-tab_2026-09-16.md issue 1.</t>
   </si>
   <si>
     <t>TST_SBLK_TC_1</t>
@@ -1109,10 +1138,16 @@
 2. Without selecting Children or Adults, click "Next".</t>
   </si>
   <si>
-    <t>[ASSUMED] Next is disabled, or clicking it surfaces a “choose an option” prompt, and the admin stays on the chooser.</t>
+    <t>Neither Children nor Adults is pre-selected and Next is natively disabled (a real disabled attribute, plus .disabled and pointer-events none), so the admin cannot advance and stays on /learner/select/new. The adult chooser /learner/adult-select/new behaves the same way. Verified live 2026-09-15.</t>
   </si>
   <si>
     <t>Not run 2026-08-22 — the radio state on first load was not recorded. Confirm during Phase 1; the same case applies to both downstream choosers.</t>
+  </si>
+  <si>
+    <t>As expected — automated. Next is natively disabled with neither option chosen (verified live 2026-09-15).</t>
+  </si>
+  <si>
+    <t>Automated (adminBulkStudentsTest_thor). 2 consecutive clean runs on Thor 2026-09-15.</t>
   </si>
   <si>
     <t>TST_SBLK_TC_2</t>
@@ -1231,6 +1266,9 @@
     <t>Verified live 2026-08-22 (screenshot bulk-activation-i18n-key.png). The button label counts the rows, so it changes as rows are added.</t>
   </si>
   <si>
+    <t>Automated (adminBulkStudentsTest_thor). 2 consecutive clean runs on Thor 2026-09-15. NOTE: the grid is a server-side draft kept per admin account, so one empty entry row only holds after the grid is emptied; the TC clears it first (admin-students-tab.md 9.5).</t>
+  </si>
+  <si>
     <t>TST_SBLK_TC_11</t>
   </si>
   <si>
@@ -1272,10 +1310,16 @@
     <t>One partial row, then one complete row</t>
   </si>
   <si>
-    <t>[ASSUMED] The button is disabled until at least one row carries both an identified student and a code, and enabled once a row is complete.</t>
+    <t>With the row empty, and with only an Activation code filled, Activate 1 code is disabled, and the row reads: Enter a student’s email or username. Once a known student’s email is entered and the field is left, First name and Last name auto-fill and Activate 1 code becomes enabled. Verified live 2026-09-15.</t>
   </si>
   <si>
     <t>Only the empty-row disabled state was verified live 2026-08-22; the enabling threshold was not exercised. Confirm during Phase 1.</t>
+  </si>
+  <si>
+    <t>As expected — automated. Code only keeps Activate disabled and the row asks for the student; a known email auto-fills the names and enables Activate (never clicked).</t>
+  </si>
+  <si>
+    <t>Automated (adminBulkStudentsTest_thor). 2 consecutive clean runs on Thor 2026-09-15. Resolves the [ASSUMED] enabling threshold.</t>
   </si>
   <si>
     <t>TST_SBLK_TC_9</t>
@@ -1352,15 +1396,21 @@
     <t>1. Enter the name containing special characters in the search box. 2. Click Search. 3. Read the returned row(s) and the rendered name.</t>
   </si>
   <si>
-    <t>First name !^(+)s95 or &amp;FName - names present on the shared school per the other team's sheet. Confirm live before running.</t>
-  </si>
-  <si>
-    <t>The matching student is returned. The term is treated as literal text rather than interpreted, and the name is rendered correctly in the result row - not HTML-escaped, truncated or corrupted. [ASSUMED]</t>
+    <t>First name cqateststu!^+s95, last name &amp;LName (cqateststu!^+s95@mailsac.com). Search terms: !^+s95 and &amp;LName.</t>
+  </si>
+  <si>
+    <t>Each search returns EXACTLY ONE row — the special characters are matched literally, not as wildcards. The name is rendered character for character in the row (not HTML-escaped, stripped or truncated) and the search banner echoes the term verbatim. Verified live 2026-09-16.</t>
   </si>
   <si>
     <t>Added 2026-09-01 from the other team's TC_STU_001, which lists special-character names as fixtures. We already cover special characters in the email field (TST_SLST_TC_7) but never in a name field. SLST is already automated, so this is cheap to add. Read-only - no data created.</t>
   </si>
   <si>
+    <t>As expected — automated. Both the !^+s95 (first name) and &amp;LName (last name) searches returned exactly the one student, names intact.</t>
+  </si>
+  <si>
+    <t>Unblocked 2026-09-16: the user created cqateststu!^+s95 &amp;LName on FCN-CHZ-PDA. Automated (adminStudentsTabTest_thor), 2 consecutive clean runs on Thor 2026-09-16, 24/24 both times.</t>
+  </si>
+  <si>
     <t>TST_SLST_TC_27</t>
   </si>
   <si>
@@ -1385,6 +1435,9 @@
     <t>Added 2026-09-01 from the other team's TC_STU_004, whose step 2 searches a partial username. Our TST_SLST_TC_8 searches a full child username only. We already prove partial matching for first name (TST_SLST_TC_3), so username was the one identifier left unverified. Read-only.</t>
   </si>
   <si>
+    <t>Blocked 2026-09-15 (user decision): FCN-CHZ-PDA holds exactly one username account (cqatestaichild1); the case needs two or more sharing a substring. Unblock: Group C SBLK_TC_1/2 creating username accounts.</t>
+  </si>
+  <si>
     <t>TST_SLST_TC_28</t>
   </si>
   <si>
@@ -1409,6 +1462,12 @@
     <t>Added 2026-09-01 from the other team's TC_STU_005, step 2. Our TST_SLST_TC_13 only toggles the checkbox and TST_SLST_TC_14 (Blocked, needs a known redeemed code) covers the success path, so the failure path was entirely unverified. This case is cheaper than TC_14 and can run today - it needs no seeded redemption. Read-only.</t>
   </si>
   <si>
+    <t>DEFECT: the search does not show a no-result state. activationCodeSearch returns HTTP 504 and the admin is redirected to /dashboard/error (Sorry! Something went wrong) — after 61.9 s on the automated run.</t>
+  </si>
+  <si>
+    <t>On Hold in automation — open bug: activation-code search returns HTTP 504 and redirects to /dashboard/error. Case is written, registered and verified, but kept OUT of the execution files so the suite is not permanently red. See .architecture/PRODUCT-QUESTIONS_students-tab_2026-09-16.md issue 3. Goes back into adminStudentsTab.json when fixed.</t>
+  </si>
+  <si>
     <t>TST_SPRF_TC_23</t>
   </si>
   <si>
@@ -1479,6 +1538,12 @@
   </si>
   <si>
     <t>Added 2026-09-01 from the other team's TC_STU_017_N1. Companion to TST_SBLK_TC_13 on the adult path. Capture the stated rules verbatim on the first live pass - inventing them would breach golden rule 2. Side-effect free provided the form is never submitted.</t>
+  </si>
+  <si>
+    <t>Rows flagged correctly (username: This must start with a letter; password: See password guidance in the info section at the top; valid row clean) — but DEFECT: Create 2 account stays enabled (no disabled attribute, pointer-events auto). Label also reads 2 account.</t>
+  </si>
+  <si>
+    <t>On Hold in automation — open bug: Create N account stays enabled while a row is invalid. Rows themselves are flagged correctly. Case is written, registered and verified, kept OUT of the execution files; Create is never clicked. See PRODUCT-QUESTIONS_students-tab_2026-09-16.md issue 2.</t>
   </si>
   <si>
     <t>TST_SBLK_TC_15</t>
@@ -3138,13 +3203,13 @@
         <v>184</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>24</v>
+        <v>185</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>177</v>
+        <v>25</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>24</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3152,10 +3217,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>180</v>
@@ -3167,28 +3232,28 @@
         <v>41</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>24</v>
+        <v>185</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>177</v>
+        <v>25</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>24</v>
+        <v>194</v>
       </c>
     </row>
     <row r="29" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3196,10 +3261,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>180</v>
@@ -3211,28 +3276,28 @@
         <v>41</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>45</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>24</v>
+        <v>185</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>177</v>
+        <v>25</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>24</v>
+        <v>194</v>
       </c>
     </row>
     <row r="30" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3240,10 +3305,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>180</v>
@@ -3255,28 +3320,28 @@
         <v>55</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>24</v>
+        <v>185</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>177</v>
+        <v>25</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>24</v>
+        <v>194</v>
       </c>
     </row>
     <row r="31" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3284,10 +3349,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>180</v>
@@ -3302,25 +3367,25 @@
         <v>19</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>24</v>
+        <v>213</v>
       </c>
     </row>
     <row r="32" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3328,13 +3393,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>17</v>
@@ -3346,25 +3411,25 @@
         <v>19</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>73</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>24</v>
+        <v>185</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>177</v>
+        <v>25</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>24</v>
+        <v>194</v>
       </c>
     </row>
     <row r="33" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3372,13 +3437,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>17</v>
@@ -3390,16 +3455,16 @@
         <v>19</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>24</v>
@@ -3408,7 +3473,7 @@
         <v>111</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="34" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3416,13 +3481,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>17</v>
@@ -3431,19 +3496,19 @@
         <v>18</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>24</v>
@@ -3460,13 +3525,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>225</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>62</v>
@@ -3475,28 +3540,28 @@
         <v>18</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>24</v>
+        <v>185</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>177</v>
+        <v>25</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>24</v>
+        <v>194</v>
       </c>
     </row>
     <row r="36" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3504,13 +3569,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>17</v>
@@ -3519,19 +3584,19 @@
         <v>18</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>24</v>
@@ -3548,13 +3613,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>244</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>239</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>48</v>
@@ -3563,28 +3628,28 @@
         <v>41</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>24</v>
+        <v>185</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>177</v>
+        <v>25</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>24</v>
+        <v>194</v>
       </c>
     </row>
     <row r="38" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3592,13 +3657,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>48</v>
@@ -3607,19 +3672,19 @@
         <v>41</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>24</v>
@@ -3636,13 +3701,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>62</v>
@@ -3651,28 +3716,28 @@
         <v>41</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>24</v>
+        <v>268</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>177</v>
+        <v>25</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>24</v>
+        <v>269</v>
       </c>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3680,13 +3745,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>17</v>
@@ -3698,16 +3763,16 @@
         <v>19</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>24</v>
@@ -3724,13 +3789,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>48</v>
@@ -3739,28 +3804,28 @@
         <v>41</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>24</v>
+        <v>185</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>177</v>
+        <v>25</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>24</v>
+        <v>194</v>
       </c>
     </row>
     <row r="42" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3768,13 +3833,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>62</v>
@@ -3783,28 +3848,28 @@
         <v>18</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>24</v>
+        <v>185</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>177</v>
+        <v>25</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>24</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3812,13 +3877,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>17</v>
@@ -3827,28 +3892,28 @@
         <v>18</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>24</v>
+        <v>185</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>177</v>
+        <v>25</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>24</v>
+        <v>194</v>
       </c>
     </row>
     <row r="44" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3856,13 +3921,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>62</v>
@@ -3871,19 +3936,19 @@
         <v>18</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>24</v>
@@ -3900,13 +3965,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>17</v>
@@ -3918,25 +3983,25 @@
         <v>19</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>24</v>
+        <v>312</v>
       </c>
     </row>
     <row r="46" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3944,13 +4009,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>48</v>
@@ -3959,19 +4024,19 @@
         <v>41</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>24</v>
@@ -3980,7 +4045,7 @@
         <v>111</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
     </row>
     <row r="47" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3988,13 +4053,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>48</v>
@@ -4006,25 +4071,25 @@
         <v>19</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>24</v>
+        <v>326</v>
       </c>
     </row>
     <row r="48" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4032,13 +4097,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>62</v>
@@ -4047,28 +4112,28 @@
         <v>41</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>24</v>
+        <v>334</v>
       </c>
     </row>
     <row r="49" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4076,13 +4141,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>17</v>
@@ -4091,19 +4156,19 @@
         <v>18</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>24</v>
@@ -4120,13 +4185,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>48</v>
@@ -4138,25 +4203,25 @@
         <v>19</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>24</v>
+        <v>348</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>177</v>
+        <v>25</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>24</v>
+        <v>349</v>
       </c>
     </row>
     <row r="51" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4164,13 +4229,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>17</v>
@@ -4179,19 +4244,19 @@
         <v>18</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>24</v>
@@ -4208,13 +4273,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>17</v>
@@ -4223,19 +4288,19 @@
         <v>18</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>24</v>
@@ -4252,13 +4317,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>17</v>
@@ -4267,19 +4332,19 @@
         <v>18</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>24</v>
@@ -4296,13 +4361,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>17</v>
@@ -4311,19 +4376,19 @@
         <v>41</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>24</v>
@@ -4340,13 +4405,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>17</v>
@@ -4358,25 +4423,25 @@
         <v>19</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>24</v>
+        <v>185</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>177</v>
+        <v>25</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>24</v>
+        <v>385</v>
       </c>
     </row>
     <row r="56" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4384,13 +4449,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>17</v>
@@ -4399,19 +4464,19 @@
         <v>41</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>24</v>
@@ -4428,13 +4493,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="C57" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>381</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>369</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>48</v>
@@ -4443,28 +4508,28 @@
         <v>41</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>24</v>
+        <v>400</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>177</v>
+        <v>25</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>24</v>
+        <v>401</v>
       </c>
     </row>
     <row r="58" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4472,13 +4537,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>387</v>
+        <v>402</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>62</v>
@@ -4487,19 +4552,19 @@
         <v>18</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>389</v>
+        <v>404</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>391</v>
+        <v>406</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>24</v>
@@ -4516,13 +4581,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>62</v>
@@ -4531,19 +4596,19 @@
         <v>41</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>24</v>
@@ -4560,13 +4625,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>62</v>
@@ -4575,19 +4640,19 @@
         <v>41</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>401</v>
+        <v>416</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>24</v>
@@ -4604,13 +4669,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>407</v>
+        <v>422</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>48</v>
@@ -4619,28 +4684,28 @@
         <v>41</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>410</v>
+        <v>425</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>24</v>
+        <v>428</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>177</v>
+        <v>25</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>24</v>
+        <v>429</v>
       </c>
     </row>
     <row r="62" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4648,13 +4713,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>48</v>
@@ -4663,28 +4728,28 @@
         <v>41</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>417</v>
+        <v>434</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>419</v>
+        <v>436</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>177</v>
+        <v>111</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>24</v>
+        <v>438</v>
       </c>
     </row>
     <row r="63" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4692,13 +4757,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>422</v>
+        <v>440</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>62</v>
@@ -4707,28 +4772,28 @@
         <v>41</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>428</v>
+        <v>446</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>24</v>
+        <v>447</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>24</v>
+        <v>448</v>
       </c>
     </row>
     <row r="64" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4736,13 +4801,13 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>429</v>
+        <v>449</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>431</v>
+        <v>451</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>17</v>
@@ -4751,19 +4816,19 @@
         <v>18</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>24</v>
@@ -4780,13 +4845,13 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>439</v>
+        <v>459</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>62</v>
@@ -4795,19 +4860,19 @@
         <v>18</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>442</v>
+        <v>462</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>444</v>
+        <v>464</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>24</v>
@@ -4824,13 +4889,13 @@
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>446</v>
+        <v>466</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>447</v>
+        <v>467</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>62</v>
@@ -4839,28 +4904,28 @@
         <v>18</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>448</v>
+        <v>468</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>451</v>
+        <v>471</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>24</v>
+        <v>473</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>24</v>
+        <v>474</v>
       </c>
     </row>
     <row r="67" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4868,13 +4933,13 @@
         <v>66</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>453</v>
+        <v>475</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>454</v>
+        <v>476</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>455</v>
+        <v>477</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>62</v>
@@ -4883,19 +4948,19 @@
         <v>18</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>456</v>
+        <v>478</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>457</v>
+        <v>479</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>458</v>
+        <v>480</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>459</v>
+        <v>481</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>460</v>
+        <v>482</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>24</v>
@@ -4912,13 +4977,13 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>461</v>
+        <v>483</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>462</v>
+        <v>484</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>439</v>
+        <v>459</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>17</v>
@@ -4927,19 +4992,19 @@
         <v>41</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>463</v>
+        <v>485</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>464</v>
+        <v>486</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>465</v>
+        <v>487</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>466</v>
+        <v>488</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>467</v>
+        <v>489</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>24</v>
@@ -4948,7 +5013,7 @@
         <v>111</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
     </row>
     <row r="69" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4956,13 +5021,13 @@
         <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>469</v>
+        <v>491</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>470</v>
+        <v>492</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>447</v>
+        <v>467</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>48</v>
@@ -4971,19 +5036,19 @@
         <v>41</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>471</v>
+        <v>493</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>472</v>
+        <v>494</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>473</v>
+        <v>495</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>475</v>
+        <v>497</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>24</v>
@@ -4999,10 +5064,10 @@
   <autoFilter ref="A1:N1"/>
   <dataValidations count="2">
     <dataValidation type="list" sqref="M10:M60">
-      <formula1>"Not Run,Pass,Fail,Blocked"</formula1>
+      <formula1>"Not Run,Pass,Fail,Blocked,On Hold"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="M2:M60">
-      <formula1>"Not Run,Pass,Fail,Blocked"</formula1>
+      <formula1>"Not Run,Pass,Fail,Blocked,On Hold"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Students/AdminApp_Students_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Students/AdminApp_Students_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="479">
   <si>
     <t>S.No.</t>
   </si>
@@ -102,7 +102,7 @@
     <t>Automated</t>
   </si>
   <si>
-    <t>Suite: adminStudentsTab | 2026-09-16: Pass across 2 runs</t>
+    <t>Suite: adminStudentsTab | Not executed in this audit - status carried over, treat as unverified</t>
   </si>
   <si>
     <t>TST_SLST_TC_2</t>
@@ -643,7 +643,7 @@
     <t>Automated (adminStudentProfileTest_thor). Passing on Thor 2026-09-15: baseline 10/10, then 11/11 after TST_SPRF_TC_12 was added.</t>
   </si>
   <si>
-    <t>Suite: adminStudentProfile | 2026-09-16: Pass across 2 runs</t>
+    <t>Suite: adminStudentProfile | Not executed in this audit - status carried over, treat as unverified</t>
   </si>
   <si>
     <t>TST_SPRF_TC_4</t>
@@ -872,38 +872,13 @@
     <t>Verified live 2026-08-22 on the child account: firstName and lastName are required and editable; username and country are disabled. On that account the disabled Location field held the literal string "undefined" rather than a country or a blank — worth raising separately as a display defect. Neither name field carries a maxlength attribute, so any length limit is server-side and unknown; do not write a boundary case until it is measured.</t>
   </si>
   <si>
-    <t>TST_SPRF_TC_13</t>
-  </si>
-  <si>
-    <t>Verify leaving the form with unsaved changes raises a confirmation</t>
+    <t>TST_SPRF_TC_12</t>
+  </si>
+  <si>
+    <t>Verify a required name field cannot be saved empty</t>
   </si>
   <si>
     <t>Logged in as school admin (testt1@mailsac.com) on Thor. School "3 July Test School 1" (key FCN-CHZ-PDA) opened from "My school accounts". Students tab is displayed. The student's View student profile page is open. The "Personal info" tab is open.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Change the First name value.
-2. Click "Cancel" (or navigate away).</t>
-  </si>
-  <si>
-    <t>Any changed value</t>
-  </si>
-  <si>
-    <t>A confirmation dialog is raised reading, verbatim: "Save changes?" / "Changes will be lost if you don’t save them" with "Cancel" and "Yes" buttons.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Copy captured free from the pre-rendered DOM 2026-08-22 (admin-shared.md §A6 trick) — the dialog was never triggered, but its text is verified. Which of Cancel/Yes discards versus saves is [ASSUMED] and must be confirmed.</t>
-  </si>
-  <si>
-    <t>Excluded - Phase 1</t>
-  </si>
-  <si>
-    <t>Out of Phase 1 automation scope.</t>
-  </si>
-  <si>
-    <t>TST_SPRF_TC_12</t>
-  </si>
-  <si>
-    <t>Verify a required name field cannot be saved empty</t>
   </si>
   <si>
     <t>1. Clear the First name field. 2. Move focus out of the field (Tab). 3. Read the message under First name and the state of Update. Do not force a submit.</t>
@@ -1069,31 +1044,6 @@
     <t>On Hold in automation — student removal is missing from the Students tab (profile and list). Awaiting product: withdrawn on purpose, or a regression? See PRODUCT-QUESTIONS_students-tab_2026-09-16.md issue 1.</t>
   </si>
   <si>
-    <t>TST_SPRF_TC_20</t>
-  </si>
-  <si>
-    <t>Verify selecting more than 50 students blocks the removal with a limit message</t>
-  </si>
-  <si>
-    <t>Logged in as school admin (testt1@mailsac.com) on Thor. School "3 July Test School 1" (key FCN-CHZ-PDA) opened from "My school accounts". Students tab is displayed. The school holds more than 50 students.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Select 51 or more students.
-2. Click "Remove from school account".</t>
-  </si>
-  <si>
-    <t>51+ selected students</t>
-  </si>
-  <si>
-    <t>The removal is refused and a dialog reads, verbatim: "You can only remove 50 students at one time" / "Please uncheck some students to continue", with a single "Close" action.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. BLOCKED at design time on FCN-CHZ-PDA — the school holds 26 students, so 51 cannot be selected. The modal copy is nevertheless verified word for word from the pre-rendered DOM (2026-08-22), so this case is short work once a school with 51+ students exists. Unblocked by &lt;SCHOOL_WITH_51_PLUS_STUDENTS&gt;.</t>
-  </si>
-  <si>
-    <t>Blocked. 2026-09-15: student removal is absent from the Students tab entirely (see TST_SPRF_TC_19), awaiting product. Original design-time reason still applies: the 50-student cap needs 51+ students; FCN-CHZ-PDA holds 27.</t>
-  </si>
-  <si>
     <t>TST_SPRF_TC_21</t>
   </si>
   <si>
@@ -1186,7 +1136,7 @@
     <t>Automated (adminBulkStudentsTest_thor). 2 consecutive clean runs on Thor 2026-09-15.</t>
   </si>
   <si>
-    <t>Suite: adminBulkStudents | 2026-09-16: Pass across 2 runs</t>
+    <t>Suite: adminBulkStudents | Not executed in this audit - status carried over, treat as unverified</t>
   </si>
   <si>
     <t>TST_SBLK_TC_2</t>
@@ -1359,65 +1309,6 @@
   </si>
   <si>
     <t>Automated (adminBulkStudentsTest_thor). 2 consecutive clean runs on Thor 2026-09-15. Resolves the [ASSUMED] enabling threshold.</t>
-  </si>
-  <si>
-    <t>TST_SBLK_TC_9</t>
-  </si>
-  <si>
-    <t>Verify the bulk-activation success dialog shows real text and not raw translation keys</t>
-  </si>
-  <si>
-    <t>A bulk activation has been submitted successfully.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Complete at least one valid row on the bulk activation page.
-2. Click "Activate N codes".
-3. Read the success dialog.</t>
-  </si>
-  <si>
-    <t>&lt;VALID_UNUSED_ACTIVATION_CODE&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The dialog should explain what happened in plain English.
-ACTUAL (defect, observed 2026-08-22): the dialog body renders three RAW UNTRANSLATED KEYS instead of text — "ADMIN.LEARNER.BULK_ACTIVATION.SUCCESS_MODAL_INFO_1", "...SUCCESS_MODAL_INFO_2" and "...SUCCESS_MODAL_INFO_3" — above a "Back to dashboard" button.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. DEFECT — raise. Captured WITHOUT running a bulk activation, by reading the pre-rendered dialog in the DOM (admin-shared.md §A6). This is a user-visible failure waiting for the first successful bulk activation. The same page also holds "An unexpected error occured." (sic — “occured”) in its Form-not-uploaded dialog.</t>
-  </si>
-  <si>
-    <t>TST_SBLK_TC_10</t>
-  </si>
-  <si>
-    <t>Verify the bulk-activation row checkbox exposes a real accessible label</t>
-  </si>
-  <si>
-    <t>1. Inspect the accessible name of the entry row's select checkbox (screen reader, or the sr-only label in the markup).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The checkbox should announce something meaningful such as “Select student row”.
-ACTUAL (defect, observed 2026-08-22): the screen-reader-only label contains the raw key "ADMIN.LEARNER.BULK_ACTIVATION.SELECT_STUDENT", so a screen-reader user hears the translation key. The key is not visible on screen, which is why it has gone unnoticed.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. DEFECT (accessibility) — raise alongside TST_SBLK_TC_9; same missing translation bundle. A third instance, "SCREEN_READER.PROCESSING_MESSAGE", appears on the individual activation page (TST_SPRF_TC_16), so this looks like one systemic gap rather than three separate typos.</t>
-  </si>
-  <si>
-    <t>TST_SBLK_TC_12</t>
-  </si>
-  <si>
-    <t>Verify a CSV that cannot be processed is rejected with a clear message</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click "Upload file" and choose a malformed or oversized CSV.
-2. Read the dialog.</t>
-  </si>
-  <si>
-    <t>TST_SBLK_TC_12_malformed.csv</t>
-  </si>
-  <si>
-    <t>The upload is refused and a dialog headed "Sorry, your file could not be uploaded" is shown, ending "If that doesn’t work, email our Customer Services team at ptsupport@cambridge.org". [ASSUMED for the specific reason line, which is populated per failure type.]</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Dialog shell captured from the pre-rendered DOM 2026-08-22. The equivalent dialog on the adult CSV page enforces a 200-record maximum with its own wording (see product-knowledge/ExperienceApp.md); whether bulk activation shares that limit is unknown.</t>
   </si>
   <si>
     <t>TST_SLST_TC_26</t>
@@ -2052,7 +1943,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P69"/>
+  <dimension ref="A1:P64"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -3922,7 +3813,7 @@
     </row>
     <row r="38" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>265</v>
@@ -3934,7 +3825,7 @@
         <v>254</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>45</v>
@@ -3955,24 +3846,24 @@
         <v>271</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>26</v>
+        <v>272</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>182</v>
+        <v>27</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>26</v>
+        <v>273</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>272</v>
+        <v>28</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>273</v>
+        <v>194</v>
       </c>
     </row>
     <row r="39" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>274</v>
@@ -3981,128 +3872,128 @@
         <v>275</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>267</v>
+        <v>21</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>280</v>
+        <v>26</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>281</v>
+        <v>26</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="D40" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G40" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="H40" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="E40" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H40" s="3" t="s">
+      <c r="I40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J40" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="I40" s="3" t="s">
+      <c r="K40" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="J40" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>288</v>
-      </c>
       <c r="L40" s="3" t="s">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>182</v>
+        <v>27</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>183</v>
+        <v>28</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
     </row>
     <row r="41" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="H41" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="I41" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G41" s="3" t="s">
+      <c r="J41" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="H41" s="3" t="s">
+      <c r="K41" s="3" t="s">
         <v>292</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>294</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>192</v>
@@ -4122,25 +4013,25 @@
     </row>
     <row r="42" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>284</v>
-      </c>
       <c r="E42" s="3" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>297</v>
@@ -4172,7 +4063,7 @@
     </row>
     <row r="43" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>301</v>
@@ -4184,7 +4075,7 @@
         <v>303</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>20</v>
@@ -4205,24 +4096,24 @@
         <v>308</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>192</v>
+        <v>26</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>202</v>
+        <v>26</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="44" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>309</v>
@@ -4234,34 +4125,34 @@
         <v>311</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H44" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="H44" s="3" t="s">
+      <c r="I44" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="I44" s="3" t="s">
+      <c r="J44" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="J44" s="3" t="s">
+      <c r="K44" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="K44" s="3" t="s">
+      <c r="L44" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="N44" s="3" t="s">
         <v>316</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>183</v>
@@ -4272,7 +4163,7 @@
     </row>
     <row r="45" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>317</v>
@@ -4281,28 +4172,28 @@
         <v>318</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H45" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J45" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="I45" s="3" t="s">
+      <c r="K45" s="3" t="s">
         <v>321</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>323</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>26</v>
@@ -4311,118 +4202,118 @@
         <v>220</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>183</v>
+        <v>222</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>184</v>
+        <v>223</v>
       </c>
     </row>
     <row r="46" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>45</v>
       </c>
       <c r="G46" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="I46" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="H46" s="3" t="s">
+      <c r="J46" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="I46" s="3" t="s">
+      <c r="K46" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="J46" s="3" t="s">
+      <c r="L46" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="N46" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>332</v>
-      </c>
       <c r="O46" s="3" t="s">
-        <v>115</v>
+        <v>183</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>117</v>
+        <v>184</v>
       </c>
     </row>
     <row r="47" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B47" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="E47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G47" s="3" t="s">
         <v>334</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>335</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>23</v>
+        <v>336</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>338</v>
+        <v>26</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>222</v>
+        <v>183</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>223</v>
+        <v>184</v>
       </c>
     </row>
     <row r="48" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>339</v>
@@ -4431,48 +4322,48 @@
         <v>340</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="G48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H48" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="H48" s="3" t="s">
+      <c r="I48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J48" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="I48" s="3" t="s">
+      <c r="K48" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="J48" s="3" t="s">
+      <c r="L48" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="K48" s="3" t="s">
+      <c r="M48" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N48" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="N48" s="3" t="s">
+      <c r="O48" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P48" s="3" t="s">
         <v>346</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="49" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>347</v>
@@ -4490,19 +4381,19 @@
         <v>20</v>
       </c>
       <c r="G49" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="H49" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="H49" s="3" t="s">
+      <c r="I49" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="I49" s="3" t="s">
+      <c r="J49" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="J49" s="3" t="s">
+      <c r="K49" s="3" t="s">
         <v>353</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>354</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>26</v>
@@ -4522,66 +4413,66 @@
     </row>
     <row r="50" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="D50" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>349</v>
-      </c>
       <c r="E50" s="3" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>21</v>
+        <v>334</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>357</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>23</v>
+        <v>358</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>360</v>
+        <v>26</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>361</v>
+        <v>26</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>362</v>
+        <v>184</v>
       </c>
     </row>
     <row r="51" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B51" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>363</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>365</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>19</v>
@@ -4590,19 +4481,19 @@
         <v>20</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="H51" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="I51" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="I51" s="3" t="s">
+      <c r="J51" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="J51" s="3" t="s">
+      <c r="K51" s="3" t="s">
         <v>368</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="L51" s="3" t="s">
         <v>26</v>
@@ -4622,37 +4513,37 @@
     </row>
     <row r="52" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>371</v>
-      </c>
       <c r="D52" s="3" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="H52" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="I52" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="I52" s="3" t="s">
+      <c r="J52" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="J52" s="3" t="s">
+      <c r="K52" s="3" t="s">
         <v>375</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>376</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>26</v>
@@ -4672,16 +4563,16 @@
     </row>
     <row r="53" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="D53" s="3" t="s">
         <v>378</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>379</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>19</v>
@@ -4690,48 +4581,48 @@
         <v>20</v>
       </c>
       <c r="G53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J53" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="H53" s="3" t="s">
+      <c r="K53" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="I53" s="3" t="s">
+      <c r="L53" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N53" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="J53" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="K53" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="L53" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M53" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="N53" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="O53" s="3" t="s">
-        <v>183</v>
+        <v>28</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>184</v>
+        <v>346</v>
       </c>
     </row>
     <row r="54" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>19</v>
@@ -4740,19 +4631,19 @@
         <v>45</v>
       </c>
       <c r="G54" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="I54" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="H54" s="3" t="s">
+      <c r="J54" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="I54" s="3" t="s">
+      <c r="K54" s="3" t="s">
         <v>389</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>391</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>26</v>
@@ -4772,40 +4663,40 @@
     </row>
     <row r="55" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G55" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="H55" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="I55" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="E55" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H55" s="3" t="s">
+      <c r="J55" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="I55" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J55" s="3" t="s">
+      <c r="K55" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="K55" s="3" t="s">
+      <c r="L55" s="3" t="s">
         <v>397</v>
-      </c>
-      <c r="L55" s="3" t="s">
-        <v>192</v>
       </c>
       <c r="M55" s="3" t="s">
         <v>27</v>
@@ -4817,12 +4708,12 @@
         <v>28</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>362</v>
+        <v>346</v>
       </c>
     </row>
     <row r="56" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>399</v>
@@ -4831,57 +4722,57 @@
         <v>400</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>45</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>182</v>
+        <v>27</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>26</v>
+        <v>408</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>183</v>
+        <v>28</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>184</v>
+        <v>29</v>
       </c>
     </row>
     <row r="57" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>394</v>
+        <v>411</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>52</v>
@@ -4890,119 +4781,119 @@
         <v>45</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>413</v>
+        <v>26</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>27</v>
+        <v>115</v>
       </c>
       <c r="N57" s="3" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="O57" s="3" t="s">
-        <v>28</v>
+        <v>115</v>
       </c>
       <c r="P57" s="3" t="s">
-        <v>362</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>26</v>
+        <v>426</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>182</v>
+        <v>220</v>
       </c>
       <c r="N58" s="3" t="s">
-        <v>26</v>
+        <v>427</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>272</v>
+        <v>222</v>
       </c>
       <c r="P58" s="3" t="s">
-        <v>273</v>
+        <v>428</v>
       </c>
     </row>
     <row r="59" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>394</v>
+        <v>431</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>401</v>
+        <v>432</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>23</v>
+        <v>434</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>26</v>
@@ -5014,45 +4905,45 @@
         <v>26</v>
       </c>
       <c r="O59" s="3" t="s">
-        <v>272</v>
+        <v>183</v>
       </c>
       <c r="P59" s="3" t="s">
-        <v>273</v>
+        <v>184</v>
       </c>
     </row>
     <row r="60" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>394</v>
+        <v>439</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>401</v>
+        <v>440</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="L60" s="3" t="s">
         <v>26</v>
@@ -5064,195 +4955,195 @@
         <v>26</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>272</v>
+        <v>183</v>
       </c>
       <c r="P60" s="3" t="s">
-        <v>273</v>
+        <v>184</v>
       </c>
     </row>
     <row r="61" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>27</v>
+        <v>220</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>28</v>
+        <v>222</v>
       </c>
       <c r="P61" s="3" t="s">
-        <v>29</v>
+        <v>455</v>
       </c>
     </row>
     <row r="62" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>115</v>
+        <v>182</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>451</v>
+        <v>26</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>115</v>
+        <v>183</v>
       </c>
       <c r="P62" s="3" t="s">
-        <v>117</v>
+        <v>184</v>
       </c>
     </row>
     <row r="63" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>45</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>460</v>
+        <v>26</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>220</v>
+        <v>115</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>222</v>
+        <v>115</v>
       </c>
       <c r="P63" s="3" t="s">
-        <v>462</v>
+        <v>117</v>
       </c>
     </row>
     <row r="64" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="L64" s="3" t="s">
         <v>26</v>
@@ -5267,256 +5158,6 @@
         <v>183</v>
       </c>
       <c r="P64" s="3" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="3">
-        <v>64</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="K65" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="L65" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M65" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="N65" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O65" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="P65" s="3" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="3">
-        <v>65</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="3">
-        <v>66</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="K67" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="L67" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M67" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="N67" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O67" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="P67" s="3" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="3">
-        <v>67</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="K68" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="L68" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M68" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="N68" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="O68" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="P68" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="3">
-        <v>68</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="K69" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="L69" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M69" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="N69" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O69" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="P69" s="3" t="s">
         <v>184</v>
       </c>
     </row>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Students/AdminApp_Students_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Students/AdminApp_Students_tab_test_cases.xlsx
@@ -102,7 +102,7 @@
     <t>Automated</t>
   </si>
   <si>
-    <t>Suite: adminStudentsTab | Not executed in this audit - status carried over, treat as unverified</t>
+    <t>Suite: adminStudentsTab | 2026-09-16: Pass across 2 runs</t>
   </si>
   <si>
     <t>TST_SLST_TC_2</t>
@@ -643,7 +643,7 @@
     <t>Automated (adminStudentProfileTest_thor). Passing on Thor 2026-09-15: baseline 10/10, then 11/11 after TST_SPRF_TC_12 was added.</t>
   </si>
   <si>
-    <t>Suite: adminStudentProfile | Not executed in this audit - status carried over, treat as unverified</t>
+    <t>Suite: adminStudentProfile | 2026-09-16: Pass across 2 runs</t>
   </si>
   <si>
     <t>TST_SPRF_TC_4</t>
@@ -1136,7 +1136,7 @@
     <t>Automated (adminBulkStudentsTest_thor). 2 consecutive clean runs on Thor 2026-09-15.</t>
   </si>
   <si>
-    <t>Suite: adminBulkStudents | Not executed in this audit - status carried over, treat as unverified</t>
+    <t>Suite: adminBulkStudents | 2026-09-16: Pass across 2 runs</t>
   </si>
   <si>
     <t>TST_SBLK_TC_2</t>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Students/AdminApp_Students_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Students/AdminApp_Students_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="479">
   <si>
     <t>S.No.</t>
   </si>
@@ -872,38 +872,13 @@
     <t>Verified live 2026-08-22 on the child account: firstName and lastName are required and editable; username and country are disabled. On that account the disabled Location field held the literal string "undefined" rather than a country or a blank — worth raising separately as a display defect. Neither name field carries a maxlength attribute, so any length limit is server-side and unknown; do not write a boundary case until it is measured.</t>
   </si>
   <si>
-    <t>TST_SPRF_TC_13</t>
-  </si>
-  <si>
-    <t>Verify leaving the form with unsaved changes raises a confirmation</t>
+    <t>TST_SPRF_TC_12</t>
+  </si>
+  <si>
+    <t>Verify a required name field cannot be saved empty</t>
   </si>
   <si>
     <t>Logged in as school admin (testt1@mailsac.com) on Thor. School "3 July Test School 1" (key FCN-CHZ-PDA) opened from "My school accounts". Students tab is displayed. The student's View student profile page is open. The "Personal info" tab is open.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Change the First name value.
-2. Click "Cancel" (or navigate away).</t>
-  </si>
-  <si>
-    <t>Any changed value</t>
-  </si>
-  <si>
-    <t>A confirmation dialog is raised reading, verbatim: "Save changes?" / "Changes will be lost if you don’t save them" with "Cancel" and "Yes" buttons.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Copy captured free from the pre-rendered DOM 2026-08-22 (admin-shared.md §A6 trick) — the dialog was never triggered, but its text is verified. Which of Cancel/Yes discards versus saves is [ASSUMED] and must be confirmed.</t>
-  </si>
-  <si>
-    <t>Excluded - Phase 1</t>
-  </si>
-  <si>
-    <t>Out of Phase 1 automation scope.</t>
-  </si>
-  <si>
-    <t>TST_SPRF_TC_12</t>
-  </si>
-  <si>
-    <t>Verify a required name field cannot be saved empty</t>
   </si>
   <si>
     <t>1. Clear the First name field. 2. Move focus out of the field (Tab). 3. Read the message under First name and the state of Update. Do not force a submit.</t>
@@ -1069,31 +1044,6 @@
     <t>On Hold in automation — student removal is missing from the Students tab (profile and list). Awaiting product: withdrawn on purpose, or a regression? See PRODUCT-QUESTIONS_students-tab_2026-09-16.md issue 1.</t>
   </si>
   <si>
-    <t>TST_SPRF_TC_20</t>
-  </si>
-  <si>
-    <t>Verify selecting more than 50 students blocks the removal with a limit message</t>
-  </si>
-  <si>
-    <t>Logged in as school admin (testt1@mailsac.com) on Thor. School "3 July Test School 1" (key FCN-CHZ-PDA) opened from "My school accounts". Students tab is displayed. The school holds more than 50 students.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Select 51 or more students.
-2. Click "Remove from school account".</t>
-  </si>
-  <si>
-    <t>51+ selected students</t>
-  </si>
-  <si>
-    <t>The removal is refused and a dialog reads, verbatim: "You can only remove 50 students at one time" / "Please uncheck some students to continue", with a single "Close" action.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. BLOCKED at design time on FCN-CHZ-PDA — the school holds 26 students, so 51 cannot be selected. The modal copy is nevertheless verified word for word from the pre-rendered DOM (2026-08-22), so this case is short work once a school with 51+ students exists. Unblocked by &lt;SCHOOL_WITH_51_PLUS_STUDENTS&gt;.</t>
-  </si>
-  <si>
-    <t>Blocked. 2026-09-15: student removal is absent from the Students tab entirely (see TST_SPRF_TC_19), awaiting product. Original design-time reason still applies: the 50-student cap needs 51+ students; FCN-CHZ-PDA holds 27.</t>
-  </si>
-  <si>
     <t>TST_SPRF_TC_21</t>
   </si>
   <si>
@@ -1359,65 +1309,6 @@
   </si>
   <si>
     <t>Automated (adminBulkStudentsTest_thor). 2 consecutive clean runs on Thor 2026-09-15. Resolves the [ASSUMED] enabling threshold.</t>
-  </si>
-  <si>
-    <t>TST_SBLK_TC_9</t>
-  </si>
-  <si>
-    <t>Verify the bulk-activation success dialog shows real text and not raw translation keys</t>
-  </si>
-  <si>
-    <t>A bulk activation has been submitted successfully.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Complete at least one valid row on the bulk activation page.
-2. Click "Activate N codes".
-3. Read the success dialog.</t>
-  </si>
-  <si>
-    <t>&lt;VALID_UNUSED_ACTIVATION_CODE&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The dialog should explain what happened in plain English.
-ACTUAL (defect, observed 2026-08-22): the dialog body renders three RAW UNTRANSLATED KEYS instead of text — "ADMIN.LEARNER.BULK_ACTIVATION.SUCCESS_MODAL_INFO_1", "...SUCCESS_MODAL_INFO_2" and "...SUCCESS_MODAL_INFO_3" — above a "Back to dashboard" button.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. DEFECT — raise. Captured WITHOUT running a bulk activation, by reading the pre-rendered dialog in the DOM (admin-shared.md §A6). This is a user-visible failure waiting for the first successful bulk activation. The same page also holds "An unexpected error occured." (sic — “occured”) in its Form-not-uploaded dialog.</t>
-  </si>
-  <si>
-    <t>TST_SBLK_TC_10</t>
-  </si>
-  <si>
-    <t>Verify the bulk-activation row checkbox exposes a real accessible label</t>
-  </si>
-  <si>
-    <t>1. Inspect the accessible name of the entry row's select checkbox (screen reader, or the sr-only label in the markup).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The checkbox should announce something meaningful such as “Select student row”.
-ACTUAL (defect, observed 2026-08-22): the screen-reader-only label contains the raw key "ADMIN.LEARNER.BULK_ACTIVATION.SELECT_STUDENT", so a screen-reader user hears the translation key. The key is not visible on screen, which is why it has gone unnoticed.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. DEFECT (accessibility) — raise alongside TST_SBLK_TC_9; same missing translation bundle. A third instance, "SCREEN_READER.PROCESSING_MESSAGE", appears on the individual activation page (TST_SPRF_TC_16), so this looks like one systemic gap rather than three separate typos.</t>
-  </si>
-  <si>
-    <t>TST_SBLK_TC_12</t>
-  </si>
-  <si>
-    <t>Verify a CSV that cannot be processed is rejected with a clear message</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click "Upload file" and choose a malformed or oversized CSV.
-2. Read the dialog.</t>
-  </si>
-  <si>
-    <t>TST_SBLK_TC_12_malformed.csv</t>
-  </si>
-  <si>
-    <t>The upload is refused and a dialog headed "Sorry, your file could not be uploaded" is shown, ending "If that doesn’t work, email our Customer Services team at ptsupport@cambridge.org". [ASSUMED for the specific reason line, which is populated per failure type.]</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Dialog shell captured from the pre-rendered DOM 2026-08-22. The equivalent dialog on the adult CSV page enforces a 200-record maximum with its own wording (see product-knowledge/ExperienceApp.md); whether bulk activation shares that limit is unknown.</t>
   </si>
   <si>
     <t>TST_SLST_TC_26</t>
@@ -2052,7 +1943,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P69"/>
+  <dimension ref="A1:P64"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -3922,7 +3813,7 @@
     </row>
     <row r="38" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>265</v>
@@ -3934,7 +3825,7 @@
         <v>254</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>45</v>
@@ -3955,24 +3846,24 @@
         <v>271</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>26</v>
+        <v>272</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>182</v>
+        <v>27</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>26</v>
+        <v>273</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>272</v>
+        <v>28</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>273</v>
+        <v>194</v>
       </c>
     </row>
     <row r="39" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>274</v>
@@ -3981,128 +3872,128 @@
         <v>275</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>267</v>
+        <v>21</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>280</v>
+        <v>26</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>281</v>
+        <v>26</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="D40" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G40" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="H40" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="E40" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H40" s="3" t="s">
+      <c r="I40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J40" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="I40" s="3" t="s">
+      <c r="K40" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="J40" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>288</v>
-      </c>
       <c r="L40" s="3" t="s">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>182</v>
+        <v>27</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>183</v>
+        <v>28</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
     </row>
     <row r="41" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="H41" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="I41" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G41" s="3" t="s">
+      <c r="J41" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="H41" s="3" t="s">
+      <c r="K41" s="3" t="s">
         <v>292</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>294</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>192</v>
@@ -4122,25 +4013,25 @@
     </row>
     <row r="42" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>284</v>
-      </c>
       <c r="E42" s="3" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>297</v>
@@ -4172,7 +4063,7 @@
     </row>
     <row r="43" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>301</v>
@@ -4184,7 +4075,7 @@
         <v>303</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>20</v>
@@ -4205,24 +4096,24 @@
         <v>308</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>192</v>
+        <v>26</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>202</v>
+        <v>26</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="44" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>309</v>
@@ -4234,34 +4125,34 @@
         <v>311</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H44" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="H44" s="3" t="s">
+      <c r="I44" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="I44" s="3" t="s">
+      <c r="J44" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="J44" s="3" t="s">
+      <c r="K44" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="K44" s="3" t="s">
+      <c r="L44" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="N44" s="3" t="s">
         <v>316</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>183</v>
@@ -4272,7 +4163,7 @@
     </row>
     <row r="45" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>317</v>
@@ -4281,28 +4172,28 @@
         <v>318</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H45" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J45" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="I45" s="3" t="s">
+      <c r="K45" s="3" t="s">
         <v>321</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>323</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>26</v>
@@ -4311,118 +4202,118 @@
         <v>220</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>183</v>
+        <v>222</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>184</v>
+        <v>223</v>
       </c>
     </row>
     <row r="46" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>45</v>
       </c>
       <c r="G46" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="I46" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="H46" s="3" t="s">
+      <c r="J46" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="I46" s="3" t="s">
+      <c r="K46" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="J46" s="3" t="s">
+      <c r="L46" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="N46" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>332</v>
-      </c>
       <c r="O46" s="3" t="s">
-        <v>115</v>
+        <v>183</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>117</v>
+        <v>184</v>
       </c>
     </row>
     <row r="47" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B47" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="E47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G47" s="3" t="s">
         <v>334</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>335</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>23</v>
+        <v>336</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>338</v>
+        <v>26</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>222</v>
+        <v>183</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>223</v>
+        <v>184</v>
       </c>
     </row>
     <row r="48" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>339</v>
@@ -4431,48 +4322,48 @@
         <v>340</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="G48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H48" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="H48" s="3" t="s">
+      <c r="I48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J48" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="I48" s="3" t="s">
+      <c r="K48" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="J48" s="3" t="s">
+      <c r="L48" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="K48" s="3" t="s">
+      <c r="M48" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N48" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="N48" s="3" t="s">
+      <c r="O48" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P48" s="3" t="s">
         <v>346</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="49" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>347</v>
@@ -4490,19 +4381,19 @@
         <v>20</v>
       </c>
       <c r="G49" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="H49" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="H49" s="3" t="s">
+      <c r="I49" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="I49" s="3" t="s">
+      <c r="J49" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="J49" s="3" t="s">
+      <c r="K49" s="3" t="s">
         <v>353</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>354</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>26</v>
@@ -4522,66 +4413,66 @@
     </row>
     <row r="50" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="D50" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>349</v>
-      </c>
       <c r="E50" s="3" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>21</v>
+        <v>334</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>357</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>23</v>
+        <v>358</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>360</v>
+        <v>26</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>361</v>
+        <v>26</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>362</v>
+        <v>184</v>
       </c>
     </row>
     <row r="51" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B51" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>363</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>365</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>19</v>
@@ -4590,19 +4481,19 @@
         <v>20</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="H51" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="I51" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="I51" s="3" t="s">
+      <c r="J51" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="J51" s="3" t="s">
+      <c r="K51" s="3" t="s">
         <v>368</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="L51" s="3" t="s">
         <v>26</v>
@@ -4622,37 +4513,37 @@
     </row>
     <row r="52" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>371</v>
-      </c>
       <c r="D52" s="3" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="H52" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="I52" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="I52" s="3" t="s">
+      <c r="J52" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="J52" s="3" t="s">
+      <c r="K52" s="3" t="s">
         <v>375</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>376</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>26</v>
@@ -4672,16 +4563,16 @@
     </row>
     <row r="53" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="D53" s="3" t="s">
         <v>378</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>379</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>19</v>
@@ -4690,48 +4581,48 @@
         <v>20</v>
       </c>
       <c r="G53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J53" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="H53" s="3" t="s">
+      <c r="K53" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="I53" s="3" t="s">
+      <c r="L53" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N53" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="J53" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="K53" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="L53" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M53" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="N53" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="O53" s="3" t="s">
-        <v>183</v>
+        <v>28</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>184</v>
+        <v>346</v>
       </c>
     </row>
     <row r="54" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>19</v>
@@ -4740,19 +4631,19 @@
         <v>45</v>
       </c>
       <c r="G54" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="I54" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="H54" s="3" t="s">
+      <c r="J54" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="I54" s="3" t="s">
+      <c r="K54" s="3" t="s">
         <v>389</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>391</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>26</v>
@@ -4772,40 +4663,40 @@
     </row>
     <row r="55" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G55" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="H55" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="I55" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="E55" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H55" s="3" t="s">
+      <c r="J55" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="I55" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J55" s="3" t="s">
+      <c r="K55" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="K55" s="3" t="s">
+      <c r="L55" s="3" t="s">
         <v>397</v>
-      </c>
-      <c r="L55" s="3" t="s">
-        <v>192</v>
       </c>
       <c r="M55" s="3" t="s">
         <v>27</v>
@@ -4817,12 +4708,12 @@
         <v>28</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>362</v>
+        <v>346</v>
       </c>
     </row>
     <row r="56" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>399</v>
@@ -4831,57 +4722,57 @@
         <v>400</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>45</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>182</v>
+        <v>27</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>26</v>
+        <v>408</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>183</v>
+        <v>28</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>184</v>
+        <v>29</v>
       </c>
     </row>
     <row r="57" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>394</v>
+        <v>411</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>52</v>
@@ -4890,119 +4781,119 @@
         <v>45</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>413</v>
+        <v>26</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>27</v>
+        <v>115</v>
       </c>
       <c r="N57" s="3" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="O57" s="3" t="s">
-        <v>28</v>
+        <v>115</v>
       </c>
       <c r="P57" s="3" t="s">
-        <v>362</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>26</v>
+        <v>426</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>182</v>
+        <v>220</v>
       </c>
       <c r="N58" s="3" t="s">
-        <v>26</v>
+        <v>427</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>272</v>
+        <v>222</v>
       </c>
       <c r="P58" s="3" t="s">
-        <v>273</v>
+        <v>428</v>
       </c>
     </row>
     <row r="59" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>394</v>
+        <v>431</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>401</v>
+        <v>432</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>23</v>
+        <v>434</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>26</v>
@@ -5014,45 +4905,45 @@
         <v>26</v>
       </c>
       <c r="O59" s="3" t="s">
-        <v>272</v>
+        <v>183</v>
       </c>
       <c r="P59" s="3" t="s">
-        <v>273</v>
+        <v>184</v>
       </c>
     </row>
     <row r="60" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>394</v>
+        <v>439</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>401</v>
+        <v>440</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="L60" s="3" t="s">
         <v>26</v>
@@ -5064,195 +4955,195 @@
         <v>26</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>272</v>
+        <v>183</v>
       </c>
       <c r="P60" s="3" t="s">
-        <v>273</v>
+        <v>184</v>
       </c>
     </row>
     <row r="61" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>27</v>
+        <v>220</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>28</v>
+        <v>222</v>
       </c>
       <c r="P61" s="3" t="s">
-        <v>29</v>
+        <v>455</v>
       </c>
     </row>
     <row r="62" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>115</v>
+        <v>182</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>451</v>
+        <v>26</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>115</v>
+        <v>183</v>
       </c>
       <c r="P62" s="3" t="s">
-        <v>117</v>
+        <v>184</v>
       </c>
     </row>
     <row r="63" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>45</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>460</v>
+        <v>26</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>220</v>
+        <v>115</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>222</v>
+        <v>115</v>
       </c>
       <c r="P63" s="3" t="s">
-        <v>462</v>
+        <v>117</v>
       </c>
     </row>
     <row r="64" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="L64" s="3" t="s">
         <v>26</v>
@@ -5267,256 +5158,6 @@
         <v>183</v>
       </c>
       <c r="P64" s="3" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="3">
-        <v>64</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="K65" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="L65" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M65" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="N65" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O65" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="P65" s="3" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="3">
-        <v>65</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="3">
-        <v>66</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="K67" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="L67" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M67" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="N67" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O67" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="P67" s="3" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="3">
-        <v>67</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="K68" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="L68" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M68" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="N68" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="O68" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="P68" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="3">
-        <v>68</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="K69" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="L69" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M69" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="N69" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O69" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="P69" s="3" t="s">
         <v>184</v>
       </c>
     </row>
